--- a/data/trans_orig/IP21-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86520</t>
+          <t>85953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90277</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>79502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85580</t>
+          <t>85555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168009</t>
+          <t>167935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175199</t>
+          <t>175239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>33103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>53289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391745</t>
+          <t>391470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404812</t>
+          <t>404794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444131</t>
+          <t>443888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459308</t>
+          <t>458753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840580</t>
+          <t>839789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>861049</t>
+          <t>860674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162637</t>
+          <t>162620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170833</t>
+          <t>170715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148082</t>
+          <t>148494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156081</t>
+          <t>155603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313977</t>
+          <t>314279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325103</t>
+          <t>325022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70546</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>647005</t>
+          <t>647104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>662654</t>
+          <t>662940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>679983</t>
+          <t>679248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>696720</t>
+          <t>697826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1332449</t>
+          <t>1331703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1355484</t>
+          <t>1356283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>86933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91693</t>
+          <t>91705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78926</t>
+          <t>79376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84950</t>
+          <t>85064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168686</t>
+          <t>168444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176455</t>
+          <t>176443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30971</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55101</t>
+          <t>56535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421105</t>
+          <t>421146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436130</t>
+          <t>436394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462157</t>
+          <t>462705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>477754</t>
+          <t>477536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890238</t>
+          <t>888804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>911225</t>
+          <t>910178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19138</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>157814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164821</t>
+          <t>164859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155876</t>
+          <t>156558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165959</t>
+          <t>165896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317626</t>
+          <t>317667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329488</t>
+          <t>329201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24456</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43167</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74783</t>
+          <t>74723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673293</t>
+          <t>673738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>690471</t>
+          <t>691059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706106</t>
+          <t>705177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>724817</t>
+          <t>724687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1385881</t>
+          <t>1385941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410466</t>
+          <t>1410625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58818</t>
+          <t>58821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>64558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120868</t>
+          <t>121660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127109</t>
+          <t>127323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>452899</t>
+          <t>452250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463618</t>
+          <t>463275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465707</t>
+          <t>465625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479494</t>
+          <t>479500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923921</t>
+          <t>923188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940683</t>
+          <t>940198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160207</t>
+          <t>160638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169013</t>
+          <t>168980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>178036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185001</t>
+          <t>184944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341417</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352659</t>
+          <t>352911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53651</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673980</t>
+          <t>673887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>688016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>715114</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>730685</t>
+          <t>731211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394341</t>
+          <t>1393674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415187</t>
+          <t>1415426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54078</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107266</t>
+          <t>106772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448410</t>
+          <t>448677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456520</t>
+          <t>456672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502692</t>
+          <t>503675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512738</t>
+          <t>512372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>955258</t>
+          <t>955797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967410</t>
+          <t>967587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140823</t>
+          <t>141518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148069</t>
+          <t>148128</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176577</t>
+          <t>176458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182765</t>
+          <t>182777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321187</t>
+          <t>321577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329522</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>648056</t>
+          <t>648105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>658410</t>
+          <t>657844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742456</t>
+          <t>741716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>754546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394890</t>
+          <t>1394103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410868</t>
+          <t>1410331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7343</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83493</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79393</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89049</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85953</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>90280</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86179</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90279</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83493</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79502</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85555</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>258</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167935</t>
+          <t>167986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175239</t>
+          <t>175192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16784</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33332</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16975</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11293</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24617</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11360</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23815</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24503</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>33103</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>32547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>53002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>452488</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>443659</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>460207</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>399112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>391470</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404794</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>392272</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>404727</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>452488</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>443888</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>458753</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839789</t>
+          <t>840076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>860674</t>
+          <t>860531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9790</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6618</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3351</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11446</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11777</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9644</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152840</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148348</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156105</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>167448</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162620</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>170715</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>162289</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>170916</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152840</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148494</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>155603</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314279</t>
+          <t>313163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325022</t>
+          <t>324970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25372</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43983</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18081</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33917</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18554</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34256</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24148</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>42726</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>47799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>70704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>677991</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>696602</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>978</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>655610</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>647104</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>662940</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>646765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>662467</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>688820</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>679248</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>697826</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1331703</t>
+          <t>1332291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1356283</t>
+          <t>1355196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6906</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2115</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5436</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6816</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83010</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79286</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84952</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90254</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86933</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91705</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86886</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>92369</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83010</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79376</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85064</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168444</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176443</t>
+          <t>176040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14772</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30533</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>22212</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15816</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31064</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15241</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>30151</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22106</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15592</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30423</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>471022</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>462595</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>478356</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>429998</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>421146</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>436394</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>422059</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>436969</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>471022</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>462705</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>477536</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888804</t>
+          <t>889779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>910178</t>
+          <t>911451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493128</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493128</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493128</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493128</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493128</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493128</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13898</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9325</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4056</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13394</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -3130,67 +3130,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>162018</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>156054</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165440</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>162435</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157814</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>164859</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>157487</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>165205</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>162018</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156558</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165896</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317667</t>
+          <t>317406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329201</t>
+          <t>329502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25642</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45340</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37653</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24586</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44096</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>50058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74723</t>
+          <t>76052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>716051</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>703933</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>723631</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>983</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>682687</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>673738</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>691059</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>672788</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>690767</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>716051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>705177</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>724687</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1385941</t>
+          <t>1384612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410625</t>
+          <t>1410606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749273</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>749273</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>749273</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>749273</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>749273</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>749273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5467</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4056</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67723</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62105</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57481</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53911</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58821</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54247</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58830</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67723</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64558</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121660</t>
+          <t>120831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>127303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22061</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12131</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7792</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18817</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7953</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18704</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9235</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23110</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>466674</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>479629</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>458936</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>452250</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>463275</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>452363</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>463114</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>465625</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>479500</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923188</t>
+          <t>923802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940198</t>
+          <t>940170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471067</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471067</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471067</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9138</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7200</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3723</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12065</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2551</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9459</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182355</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178357</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185087</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165503</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160638</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168980</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>160225</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182355</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178036</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>184944</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>341074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352911</t>
+          <t>352274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14379</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29947</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15132</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29261</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15183</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29522</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>13633</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29319</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32566</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>52655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>724147</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714897</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>730465</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>681920</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>673887</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>688016</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>673626</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>724147</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>715525</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>731211</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393674</t>
+          <t>1395337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1415426</t>
+          <t>1415811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703148</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7573</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7962</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8881</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54673</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49159</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59891</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54042</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,16%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114569</t>
+          <t>101431</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106772</t>
+          <t>94609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,74 +5875,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9969</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7757</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12944</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -5950,22 +5950,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>468704</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>463456</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>472256</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>453816</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>448677</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>456672</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>426066</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>421274</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>428872</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>97,69%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>508862</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>503675</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>512372</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,22 +6063,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>962678</t>
+          <t>894772</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>955797</t>
+          <t>888267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>967587</t>
+          <t>899256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459278</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431243</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>975897</t>
+          <t>906922</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>975897</t>
+          <t>906922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>975897</t>
+          <t>906922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1423</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8033</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166127</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162378</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>145798</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>141518</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148128</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180759</t>
+          <t>146317</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176458</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182777</t>
+          <t>148747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>326557</t>
+          <t>312444</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321577</t>
+          <t>307288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329903</t>
+          <t>315423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15402</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31376</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>689504</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>681837</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>694193</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>925</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>654292</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>648105</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>657844</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>749511</t>
+          <t>619142</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741716</t>
+          <t>613609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754546</t>
+          <t>622996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1403804</t>
+          <t>1308647</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394103</t>
+          <t>1299618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410331</t>
+          <t>1315008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425479</t>
+          <t>1328807</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425479</t>
+          <t>1328807</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425479</t>
+          <t>1328807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
